--- a/docs/26-2/data/ICOK_1팀_담당산업_스크리닝.xlsx
+++ b/docs/26-2/data/ICOK_1팀_담당산업_스크리닝.xlsx
@@ -1187,9 +1187,9 @@
           <t>2차전지·소재</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>미기재</t>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>배준서</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1216,9 +1216,9 @@
           <t>소프트웨어·인터넷·게임</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>미기재</t>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>배준서</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>미기재</t>
+          <t>배준서</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>미기재</t>
+          <t>배준서</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1691,7 +1691,7 @@
     <row r="29" ht="16" customHeight="1">
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2차전지·소재 · 소프트웨어·인터넷·게임 · 지주는 담당자와 제출일이 비어 있다. 팀장이 확인한다.</t>
+          <t>배준서 팀장이 2차전지·소재와 소프트웨어·인터넷·게임 2개를 겸임한다. 지주는 팀 2 팀장이 맡았으므로 담당 산업 6개에 팀 1 인원은 4명이다. 1인 1산업 전제가 성립하지 않는다.</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,11 @@
           <t>담당자</t>
         </is>
       </c>
-      <c r="E4" s="34" t="n"/>
+      <c r="E4" s="34" t="inlineStr">
+        <is>
+          <t>배준서</t>
+        </is>
+      </c>
       <c r="F4" s="35" t="n"/>
       <c r="G4" s="30" t="inlineStr">
         <is>
@@ -7758,7 +7762,11 @@
           <t>담당자</t>
         </is>
       </c>
-      <c r="E4" s="34" t="n"/>
+      <c r="E4" s="34" t="inlineStr">
+        <is>
+          <t>배준서</t>
+        </is>
+      </c>
       <c r="F4" s="35" t="n"/>
       <c r="G4" s="30" t="inlineStr">
         <is>
